--- a/Result/checksun_type/工程設計.xlsx
+++ b/Result/checksun_type/工程設計.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>29.72</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>29.82</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>29.84</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>29.82</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>29.84</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>127333994.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>136119460.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>136119460.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>180700080.8</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>145391726.86</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>145391726.86</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-613552.485242337</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>127333994</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>127333994.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>29.47</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>29.81</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>29.84</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>29.81</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>29.84</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>96388822.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>138332873.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>138332873.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>180043930.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>147065410.9</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>147065410.9</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>2060029.688120633</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>96388822</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>96388822.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>29.33</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>29.85</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>29.87</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>29.85</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>29.87</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>230366989.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>203567123.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>203567123.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>176748876.3</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>147814262.16</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>147814262.16</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>9121414.446920574</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>230366989</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>230366989.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>29.27</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>29.86</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>29.88</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>29.86</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>29.88</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>115162110.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>195906349.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>195906349.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>159890084.4</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>146325446.68</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>146325446.68</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>4528538.550673336</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>115162110</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>115162110.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>29.48</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>29.93</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>29.91</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>29.93</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>29.91</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>111345387.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>224691822.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>224691822.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>155503621.9</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>147839532.26</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>147839532.26</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>10148933.64351037</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>111345387</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>111345387.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>29.69</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>29.98</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>29.95</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>29.95</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>138401058.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>225280701.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>225280701.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>153817007.8</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>152621564.4</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>152621564.4</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>18224542.18172359</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>138401058</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>138401058.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>30.03</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>30.01</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>30.03</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>30.01</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>422560072.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>221754987.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>221754987.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>148259755.3</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>165846039.22</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>165846039.22</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>26211427.40839526</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>422560072</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>422560072.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>30.09</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>30.1</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>30.03</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>30.03</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>192063122.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>149930629.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>149930629.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>120348042.8</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>159096343.36</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>159096343.36</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>6239532.396197796</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>192063122</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>192063122.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>30.09</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>30.11</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>30.03</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>30.11</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>30.03</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>259089472.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>123873819.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>123873819</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>112679035.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>157358151.42</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>157358151.42</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>2181515.150337219</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>259089472</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>259089472.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>29.97</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>30.08</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>30.02</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>30.08</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>30.02</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>114289782.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>86315421.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>86315421.59999999</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>100819006.9</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>155312221.68</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>155312221.68</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-10874958.24197567</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>114289782</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>114289782.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>29.93</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>30.04</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>30.02</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>30.02</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>120772490.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>82353314.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>82353314.40000001</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>100638773.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>158831737.24</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>158831737.24</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-13624419.22235207</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>120772490</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>120772490.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>39.62</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>39.4</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>40.71</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>40.71</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>54337.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>16739.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>16739.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>13814.0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>12554.74</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>12554.74</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>2974.684800845385</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>54337</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>54337.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>39.02</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>39.34</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>40.74</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>39.34</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>40.74</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>10062.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>8003.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>8003</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>9548.0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>12075.34</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>12075.34</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-487.1305148239862</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>10062</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>10062.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>38.76000000000001</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>39.35</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>40.83</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>40.83</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>4288.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>9006.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>9006</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>9246.8</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>12404.82</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>12404.82</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-671.433447393656</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>4288</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>4288.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>38.72</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>39.43</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>40.93</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>39.43</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>40.93</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>8716.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>11437.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>11437.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>9715.7</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>12725.54</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>12725.54</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-292.1007279434089</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>8716</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>8716.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>38.88</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>39.53</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>41.03</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>39.53</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>41.03</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>6295.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>11082.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>11082.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>9627.1</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>12959.38</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>12959.38</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-214.193245587936</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>6295</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>6295.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>39.07000000000001</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>39.64</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>41.13</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>39.64</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>41.13</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>10654.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>10888.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>10888.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>9749.4</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>13307.86</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>13307.86</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>164.1457736908815</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>10654</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>10654.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>39.33</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>39.77</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>41.25</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>41.25</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>15077.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>11093.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>11093</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>10023.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>14444.66</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>14444.66</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>231.7320236002288</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>15077</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>15077.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>39.48</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>39.89</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>41.36</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>39.89</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>41.36</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>16444.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>9487.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>9487.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>10087.0</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>15169.26</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>15169.26</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-153.8851916578515</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>16444</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>16444.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>39.54</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>39.98</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>41.45</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>41.45</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>6941.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>7994.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>7994.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>9181.0</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>15189.72</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>15189.72</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-845.7353137530426</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>6941</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>6941.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>39.45</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>40.05</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>41.52</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>40.05</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>41.52</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>5326.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>8172.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>8172</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>9082.4</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>15581.78</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>15581.78</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-785.7092269692785</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>5326</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>5326.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>39.32000000000001</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>40.08</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>41.6</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>40.08</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>41.6</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>11677.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>8610.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>8610.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>10561.0</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>16312.34</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>16312.34</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-498.8609163149977</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>11677</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>11677.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>25.34</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>28.04</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>28.51</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>28.51</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>2135.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>840.4</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>840.4</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>800.1</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>0</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-19.60460430157423</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>2135</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>2135.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>25.99</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>28.2</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>28.63</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>28.63</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>1285.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>467.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>467.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>632.9</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>0</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-139.9302155402339</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>1285</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>1285.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>26.5</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>28.34</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>28.74</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>28.74</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>160.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>392.2</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>392.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>584.6</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>0</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-215.7550096118822</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>160</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>26.86</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>28.49</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>28.84</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>28.49</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>28.84</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>406.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>427.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>427.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>762.4</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>0</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-195.8348936566698</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>406</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>406.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>27.2</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>28.61</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>28.96</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>28.96</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>216.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>663.6</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>663.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>970.6</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>0</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-186.7406246614853</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>216</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>216.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>27.35</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>28.69</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>29.02</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>28.69</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>29.02</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>270.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>759.8</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>759.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>1025.2</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>0</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-146.7223609304546</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>270</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>270.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>27.59</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>28.77</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>29.05</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>28.77</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>29.05</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>909.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>798.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>798.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>1511.3</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>0</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-90.09904271003711</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>909</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>909.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>27.68</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>28.8</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>29.09</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>29.09</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>335.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>777.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>777</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>1962.7</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>0</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-74.45505086979642</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>335</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>335.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>27.97</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>28.86</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>29.12</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>28.86</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>29.12</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>1588.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>1097.6</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>1097.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>2273.6</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>0</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>12.05261786161145</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>1588</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>1588.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>28.79</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>28.9</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>29.21</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>29.21</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>697.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>1277.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>1277.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>2136.9</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>0</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>0.9545511257081216</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>697</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>697.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>29.65</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>28.9</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>29.36</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>29.36</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>463.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>1290.6</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>1290.6</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>2149.3</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>0</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>80.53036467707079</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>463</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>463.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>661.0</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>693.85</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>757.74</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>693.85</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>757.74</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>712958.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>792037.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>792037</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>1109041.5</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>1587746.18</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>1587746.18</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-180463.9620508341</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>712958</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>712958.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>661.2</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>698.65</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>763.12</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>698.65</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>763.12</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>625808.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>1047539.2</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>1047539.2</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>1197029.2</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>1609718.98</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>1609718.98</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-173323.4371483272</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>625808</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>625808.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>654.4</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>701.8</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>768.9</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>701.8</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>768.9</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>643959.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>1163874.8</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>1163874.8</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>1469582.0</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>1641057.24</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>1641057.24</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-147595.0645323058</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>643959</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>643959.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>657.6</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>705.65</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>775.68</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>705.65</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>775.6799999999999</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>706601.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>1264658.6</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>1264658.6</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>1638238.9</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>1667740.04</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>1667740.04</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-107513.7442046928</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>706601</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>706601.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>657.8</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>709.9</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>781.92</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>709.9</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>781.92</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>1270859.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>1337944.8</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>1337944.8</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>1646579.6</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>1693766.7</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>1693766.7</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-53126.58144364925</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>1270859</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>1270859.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>659.8</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>713.75</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>787.68</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>713.75</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>787.6799999999999</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>1990469.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>1426046.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>1426046</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>1661220.1</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>1766700.72</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>1766700.72</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-33989.47101917118</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>1990469</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>1990469.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>653.2</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>720.2</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>792.16</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>720.2</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>792.16</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>1207486.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>1346519.2</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>1346519.2</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>1548234.4</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>1812003.46</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>1812003.46</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-82537.90359066054</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>1207486</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>1207486.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>655.4</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>728.45</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>796.64</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>728.45</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>796.64</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>1147878.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>1775289.2</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>1775289.2</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>1535904.2</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>1855325.14</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>1855325.14</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-65053.98927883594</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>1147878</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>1147878.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>659.0</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>736.75</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>802.06</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>736.75</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>802.0599999999999</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>1073032.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>2011819.2</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>2011819.2</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>1515893.9</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>1946359.3</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>1946359.3</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-31367.04064484267</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>1073032</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>1073032.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>679.8</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>747.95</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>808.66</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>747.95</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>808.66</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>1711365.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>1955214.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>1955214.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>1550532.2</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>2038998.2</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>2038998.2</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>25896.6374267491</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>1711365</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>1711365.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>694.0</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>757.8</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>812.84</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>757.8</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>812.84</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>1592835.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>1896394.2</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>1896394.2</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>1630314.3</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>2070739.62</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>2070739.62</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>38384.19047806808</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>1592835</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>1592835.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>165.6</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>163.02</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>160.83</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>163.02</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>160.83</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>74566654.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>58486136.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>58486136.8</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>58606873.6</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>70642832.02</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>70642832.02</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-1307560.096186429</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>74566654</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>74566654.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>163.7</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>162.93</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>160.46</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>162.93</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>160.46</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>42057189.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>51280880.2</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>51280880.2</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>57575110.0</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>70368392.78</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>70368392.78</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-2977612.849109128</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>42057189</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>42057189.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>162.4</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>163.1</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>160.23</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>163.1</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>160.23</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>86690785.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>57113679.2</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>57113679.2</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>64547068.7</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>70595791.64</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>70595791.64</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-1773902.21581623</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>86690785</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>86690785.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>161.6</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>163.32</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>160.05</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>163.32</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>160.05</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>60623888.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>52450873.4</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>52450873.4</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>60032236.0</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>69475167.82</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>69475167.81999999</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-4773132.94626151</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>60623888</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>60623888.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>160.4</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>163.85</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>159.88</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>163.85</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>159.88</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>28492168.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>47694181.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>47694181</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>56493562.8</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>68696315.04</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>68696315.04000001</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-6094397.420245431</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>28492168</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>28492168.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>159.4</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>164.42</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>159.69</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>164.42</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>159.69</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>38540371.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>58727610.4</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>58727610.4</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>57494793.8</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>69451049.8</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>69451049.8</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-4321576.760927983</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>38540371</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>38540371.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>159.0</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>164.95</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>159.6</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>164.95</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>159.6</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>71221184.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>63869339.8</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>63869339.8</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>58008720.2</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>70188106.76</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>70188106.76000001</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-2711226.970441341</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>71221184</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>71221184.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>158.9</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>165.38</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>159.41</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>165.38</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>159.41</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>63376756.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>71980458.2</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>71980458.2</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>59415753.1</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>69152957.06</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>69152957.06</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-3815413.413658947</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>63376756</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>63376756.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>159.3</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>165.7</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>159.21</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>165.7</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>159.21</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>36840426.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>67613598.6</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>67613598.59999999</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>63171366.2</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>68561486.4</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>68561486.40000001</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-4416083.42491056</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>36840426</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>36840426.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>160.8</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>166.2</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>159.08</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>166.2</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>159.08</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>83659315.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>65292944.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>65292944.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>63664049.4</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>69466030.4</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>69466030.40000001</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-2273287.961523205</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>83659315</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>83659315.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>162.4</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>166.95</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>158.97</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>166.95</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>158.97</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>64249018.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>56261977.2</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>56261977.2</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>58685909.5</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>68228488.76</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>68228488.76000001</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-4147272.265201129</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>64249018</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>64249018.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
